--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486388_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486388_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. GRANGER</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2044</v>
+        <v>8.223000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7711</v>
+        <v>6.9988</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4333</v>
+        <v>1.2242</v>
       </c>
       <c r="G2" t="n">
-        <v>8.012600000000001</v>
+        <v>4.3064</v>
       </c>
       <c r="H2" t="n">
-        <v>6.2316</v>
+        <v>2.1955</v>
       </c>
       <c r="I2" t="n">
-        <v>1.781</v>
+        <v>2.1109</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9832</v>
+        <v>3.3201</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9273</v>
+        <v>1.0402</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0559</v>
+        <v>2.2799</v>
       </c>
       <c r="M2" t="n">
-        <v>2.0294</v>
+        <v>0.9863</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3043</v>
+        <v>1.1553</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7251</v>
+        <v>-0.1689</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0.435</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0035</v>
+        <v>-0.0553</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6802</v>
+        <v>0.2464</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6837</v>
+        <v>-0.3016</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1952</v>
+        <v>4.4069</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1952</v>
+        <v>4.5199</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>J. GRANGER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0023</v>
+        <v>7.8999</v>
       </c>
       <c r="E3" t="n">
-        <v>6.148</v>
+        <v>5.4358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8542999999999999</v>
+        <v>2.4641</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3064</v>
+        <v>8.012600000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1955</v>
+        <v>6.2316</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1109</v>
+        <v>1.781</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3201</v>
+        <v>5.9832</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0402</v>
+        <v>4.9273</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2799</v>
+        <v>1.0559</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9863</v>
+        <v>2.0294</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1553</v>
+        <v>1.3043</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1689</v>
+        <v>0.7251</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.276</v>
+        <v>-0.3079</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6044</v>
+        <v>0.3449</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6715</v>
+        <v>-0.6528</v>
       </c>
       <c r="V3" t="n">
-        <v>4.4069</v>
+        <v>0.1952</v>
       </c>
       <c r="W3" t="n">
-        <v>4.5199</v>
+        <v>0.1952</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4195</v>
+        <v>2.149</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3391</v>
+        <v>-0.2706</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7587</v>
+        <v>2.4196</v>
       </c>
       <c r="G4" t="n">
         <v>1.1846</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6524</v>
+        <v>0.3818</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0649</v>
+        <v>0.0036</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7173</v>
+        <v>0.3782</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2875</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9489</v>
+        <v>1.4452</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1156</v>
+        <v>2.5194</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1666</v>
+        <v>-1.0742</v>
       </c>
       <c r="G5" t="n">
         <v>2.4283</v>
@@ -844,13 +844,13 @@
         <v>0.435</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6714</v>
+        <v>-0.1751</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2812</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0136</v>
+        <v>0.106</v>
       </c>
       <c r="V5" t="n">
         <v>-1.243</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8732</v>
+        <v>1.3601</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7693</v>
+        <v>1.9384</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1039</v>
+        <v>-0.5783</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6061</v>
+        <v>1.8624</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7942</v>
+        <v>1.7031</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1881</v>
+        <v>0.1594</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1468</v>
+        <v>1.1581</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5329</v>
+        <v>1.0434</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.6797</v>
+        <v>0.1147</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7529</v>
+        <v>0.7043</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2612</v>
+        <v>0.6597</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4916</v>
+        <v>0.0446</v>
       </c>
       <c r="P6" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6029</v>
+        <v>-1.1548</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2139</v>
+        <v>-0.3497</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.389</v>
+        <v>-0.8051</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.833</v>
+        <v>1.049</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5346</v>
+        <v>2.0461</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7016</v>
+        <v>-0.9971</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8624</v>
+        <v>2.6393</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7031</v>
+        <v>2.3477</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1594</v>
+        <v>0.2917</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1581</v>
+        <v>2.0665</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0434</v>
+        <v>1.6059</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1147</v>
+        <v>0.4606</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7043</v>
+        <v>0.5728</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6597</v>
+        <v>0.7417</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0446</v>
+        <v>-0.1689</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6819</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.0204</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9284</v>
+        <v>-0.067</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.3729</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.13</v>
+        <v>-2.3729</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7561</v>
+        <v>0.8539</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5991</v>
+        <v>0.6575</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.843</v>
+        <v>0.1964</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6393</v>
+        <v>0.6061</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3477</v>
+        <v>1.7942</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2917</v>
+        <v>-1.1881</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0665</v>
+        <v>-0.1468</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6059</v>
+        <v>1.5329</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4606</v>
+        <v>-1.6797</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5728</v>
+        <v>0.7529</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7417</v>
+        <v>0.2612</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1689</v>
+        <v>0.4916</v>
       </c>
       <c r="P8" t="n">
         <v>0.87</v>
@@ -1078,22 +1078,22 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3803</v>
+        <v>-0.6222</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4675</v>
+        <v>-0.3256</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0871</v>
+        <v>-0.2965</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.3729</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3729</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0221</v>
+        <v>-0.5452</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2435</v>
+        <v>0.2002</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2214</v>
+        <v>-0.7454</v>
       </c>
       <c r="G9" t="n">
         <v>2.0135</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.079</v>
+        <v>-0.6462</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0601</v>
+        <v>0.0168</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1391</v>
+        <v>-0.663</v>
       </c>
       <c r="V9" t="n">
         <v>-1.695</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8173</v>
+        <v>-1.6575</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2397</v>
+        <v>-0.8779</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.057</v>
+        <v>-0.7796</v>
       </c>
       <c r="G10" t="n">
         <v>0.8756</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8976</v>
+        <v>0.0574</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2762</v>
+        <v>0.1586</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3787</v>
+        <v>-0.1013</v>
       </c>
       <c r="V10" t="n">
         <v>-2.3729</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6691</v>
+        <v>-1.7615</v>
       </c>
       <c r="E11" t="n">
         <v>-1.1418</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5273</v>
+        <v>-0.6198</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4496</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1542</v>
+        <v>-0.2466</v>
       </c>
       <c r="T11" t="n">
         <v>-0.2055</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0513</v>
+        <v>-0.0412</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9754</v>
+        <v>-2.0756</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7083</v>
+        <v>-0.9318</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2671</v>
+        <v>-1.1438</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7487</v>
@@ -1390,13 +1390,13 @@
         <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2038</v>
+        <v>-0.304</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5516</v>
+        <v>0.3281</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7554</v>
+        <v>-0.6321</v>
       </c>
       <c r="V12" t="n">
         <v>0.9347</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.5977</v>
+        <v>16.9403</v>
       </c>
       <c r="E13" t="n">
-        <v>16.2317</v>
+        <v>16.5741</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3661999999999999</v>
+        <v>0.3660999999999996</v>
       </c>
       <c r="G13" t="n">
         <v>22.7305</v>
@@ -1438,7 +1438,7 @@
         <v>19.1286</v>
       </c>
       <c r="I13" t="n">
-        <v>3.602</v>
+        <v>3.601999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>15.1898</v>
@@ -1468,13 +1468,13 @@
         <v>7.612500000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.503000000000001</v>
+        <v>-3.1603</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4266000000000002</v>
+        <v>-0.08400000000000013</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0765</v>
+        <v>-3.0764</v>
       </c>
       <c r="V13" t="n">
         <v>-2.6297</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3929</v>
+        <v>1.2618</v>
       </c>
       <c r="E14" t="n">
-        <v>2.499</v>
+        <v>2.2755</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1062</v>
+        <v>-1.0137</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0148</v>
@@ -1546,13 +1546,13 @@
         <v>0.6525</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2347</v>
+        <v>0.1036</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2091</v>
+        <v>-0.0144</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0256</v>
+        <v>0.1181</v>
       </c>
       <c r="V14" t="n">
         <v>1.5204</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1955</v>
+        <v>0.9843</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2823</v>
+        <v>0.9529</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0868</v>
+        <v>0.0314</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3439</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5481</v>
+        <v>0.2406</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8784</v>
+        <v>-0.2079</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3303</v>
+        <v>0.4485</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1526</v>
+        <v>0.5945</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8994</v>
+        <v>-0.4523</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0519</v>
+        <v>1.0468</v>
       </c>
       <c r="G16" t="n">
         <v>-1.7136</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6988</v>
+        <v>-0.2569</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8784</v>
+        <v>-0.4314</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1796</v>
+        <v>0.1745</v>
       </c>
       <c r="V16" t="n">
         <v>1.695</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7762</v>
+        <v>-0.549</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1431</v>
+        <v>1.0584</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9193</v>
+        <v>-1.6074</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2408</v>
+        <v>-2.5398</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.3142</v>
+        <v>-2.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0734</v>
+        <v>-0.4813</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3259</v>
+        <v>-0.3347</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9363</v>
+        <v>-0.9117</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2622</v>
+        <v>0.577</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5668</v>
+        <v>-2.2051</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3779</v>
+        <v>-1.1468</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1889</v>
+        <v>-1.0583</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9421</v>
+        <v>0.316</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8172</v>
+        <v>0.2632</v>
       </c>
       <c r="U17" t="n">
-        <v>0.125</v>
+        <v>0.0529</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. SMITH</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3228</v>
+        <v>-0.6914</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.046</v>
+        <v>0.9196</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2768</v>
+        <v>-1.611</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.145</v>
+        <v>-1.2408</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4995</v>
+        <v>-2.3142</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6456</v>
+        <v>1.0734</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.2467</v>
+        <v>0.3259</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0881</v>
+        <v>-0.9363</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.1587</v>
+        <v>1.2622</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8983</v>
+        <v>-1.5668</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4114</v>
+        <v>-1.3779</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4869</v>
+        <v>-0.1889</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6525</v>
+        <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3448</v>
+        <v>1.0269</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1583</v>
+        <v>0.5936</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1865</v>
+        <v>0.4332</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>-1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4808</v>
+        <v>-1.7558</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5116</v>
+        <v>-1.0479</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.9924</v>
+        <v>-0.7079</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.0322</v>
+        <v>-1.7679</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2656</v>
+        <v>-2.05</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7665999999999999</v>
+        <v>0.2821</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7005</v>
+        <v>-0.4967</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7387</v>
+        <v>-1.0521</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>0.5554</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3318</v>
+        <v>-1.2712</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5269</v>
+        <v>-0.9978</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.2733</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.305</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7265</v>
+        <v>0.4047</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9972</v>
+        <v>0.4939</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2708</v>
+        <v>-0.0892</v>
       </c>
       <c r="V19" t="n">
         <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>3.3899</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>K. SMITH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9132</v>
+        <v>-2.4635</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0592</v>
+        <v>-0.9401</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.854</v>
+        <v>-1.5234</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5398</v>
+        <v>-4.145</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0585</v>
+        <v>-1.4995</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4813</v>
+        <v>-2.6456</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3347</v>
+        <v>-2.2467</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9117</v>
+        <v>-0.0881</v>
       </c>
       <c r="L20" t="n">
-        <v>0.577</v>
+        <v>-2.1587</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2051</v>
+        <v>-1.8983</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1468</v>
+        <v>-1.4114</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0583</v>
+        <v>-0.4869</v>
       </c>
       <c r="P20" t="n">
-        <v>1.305</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0481</v>
+        <v>1.2041</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8544</v>
+        <v>1.2642</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1937</v>
+        <v>-0.0601</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3698</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
         <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0474</v>
+        <v>-2.5419</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1596</v>
+        <v>1.394</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8877</v>
+        <v>-3.9359</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7679</v>
+        <v>-3.0322</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.05</v>
+        <v>-2.2656</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2821</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4967</v>
+        <v>-0.7005</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0521</v>
+        <v>-0.7387</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5554</v>
+        <v>0.0382</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2712</v>
+        <v>-2.3318</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9978</v>
+        <v>-1.5269</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2733</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5225</v>
+        <v>-1.305</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1131</v>
+        <v>0.6654</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3822</v>
+        <v>0.8797</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2691</v>
+        <v>-0.2142</v>
       </c>
       <c r="V21" t="n">
         <v>1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>3.3899</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1678</v>
+        <v>-2.8827</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9203</v>
+        <v>-0.6968</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2476</v>
+        <v>-2.1859</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1062</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3014</v>
+        <v>-0.0162</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1935</v>
+        <v>0.03</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7602</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1929</v>
+        <v>-3.6876</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4702</v>
+        <v>-1.8004</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7226</v>
+        <v>-1.8871</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9794</v>
+        <v>-2.8467</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.718</v>
+        <v>-0.6905</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2614</v>
+        <v>-2.1563</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2581</v>
+        <v>-0.797</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3346</v>
+        <v>0.7879</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0765</v>
+        <v>-1.5849</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-2.0497</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3834</v>
+        <v>-1.4783</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3379</v>
+        <v>-0.5714</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>1.699</v>
+        <v>-0.2106</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6802</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0188</v>
+        <v>-0.2947</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.2599</v>
+        <v>-0.1952</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4552</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4377</v>
+        <v>-4.1216</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2475</v>
+        <v>-2.029</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1903</v>
+        <v>-2.0925</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8467</v>
+        <v>-1.9794</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6905</v>
+        <v>-1.718</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1563</v>
+        <v>-0.2614</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.797</v>
+        <v>-1.2581</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7879</v>
+        <v>-1.3346</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5849</v>
+        <v>0.0765</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0497</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4783</v>
+        <v>-0.3834</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5714</v>
+        <v>-0.3379</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9608</v>
+        <v>0.7703</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3629</v>
+        <v>0.1214</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5979</v>
+        <v>0.6489</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1952</v>
+        <v>-2.2599</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1952</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-16.5978</v>
+        <v>-15.8529</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3661999999999994</v>
+        <v>-0.3661000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.2318</v>
+        <v>-15.4866</v>
       </c>
       <c r="G25" t="n">
         <v>-22.7303</v>
@@ -2374,13 +2374,13 @@
         <v>-19.1287</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.6019</v>
+        <v>-3.601900000000001</v>
       </c>
       <c r="J25" t="n">
         <v>-7.540699999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.417300000000001</v>
+        <v>-7.417299999999999</v>
       </c>
       <c r="L25" t="n">
         <v>-0.1234000000000002</v>
@@ -2395,22 +2395,22 @@
         <v>-3.4787</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.551115123125783e-17</v>
+        <v>-5.551115123125783e-16</v>
       </c>
       <c r="Q25" t="n">
         <v>-7.6127</v>
       </c>
       <c r="R25" t="n">
-        <v>7.6125</v>
+        <v>7.612499999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>3.503</v>
+        <v>4.2479</v>
       </c>
       <c r="T25" t="n">
-        <v>3.0766</v>
+        <v>3.0764</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4264</v>
+        <v>1.1716</v>
       </c>
       <c r="V25" t="n">
         <v>2.6299</v>
@@ -2419,7 +2419,7 @@
         <v>11.7109</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.081200000000001</v>
+        <v>-9.081199999999999</v>
       </c>
     </row>
   </sheetData>
